--- a/Side Bar Files/GWD Data/PVC wo Trench PRICE.xlsx
+++ b/Side Bar Files/GWD Data/PVC wo Trench PRICE.xlsx
@@ -844,7 +844,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{748D2CE5-7A32-4556-B2EB-E6499882BAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1A9378D-6325-4B37-B471-9B19486BBAA6}">
   <dimension ref="A1:F265"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/PVC wo Trench PRICE.xlsx
+++ b/Side Bar Files/GWD Data/PVC wo Trench PRICE.xlsx
@@ -844,7 +844,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1A9378D-6325-4B37-B471-9B19486BBAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A8D495A-D27D-430A-B748-8F8D88D9BAA6}">
   <dimension ref="A1:F265"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
